--- a/eval-suite/cases/001_dwl_con_pu_any_f/mapping.xlsx
+++ b/eval-suite/cases/001_dwl_con_pu_any_f/mapping.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2280,12 +2280,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -2326,12 +2320,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -2372,12 +2360,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -2418,12 +2400,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>赋值</t>

--- a/eval-suite/cases/001_dwl_con_pu_any_f/mapping.xlsx
+++ b/eval-suite/cases/001_dwl_con_pu_any_f/mapping.xlsx
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
